--- a/Data/ShopData.xlsx
+++ b/Data/ShopData.xlsx
@@ -1,22 +1,55 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12375"/>
+    <workbookView windowWidth="27945" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="5">
+  <si>
+    <t>#</t>
+  </si>
+  <si>
+    <t>ID</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>int</t>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
@@ -941,9 +974,68 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
-  <sheetData/>
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4" outlineLevelCol="2"/>
+  <cols>
+    <col min="3" max="3" width="18.125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <v>2</v>
+      </c>
+      <c r="C4">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5">
+        <v>3</v>
+      </c>
+      <c r="C5">
+        <v>33</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>

--- a/Data/ShopData.xlsx
+++ b/Data/ShopData.xlsx
@@ -29,21 +29,24 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="6">
   <si>
     <t>#</t>
   </si>
   <si>
-    <t>ID</t>
+    <t>Name</t>
   </si>
   <si>
-    <t>Description</t>
+    <t>Cost</t>
+  </si>
+  <si>
+    <t>ImgPath</t>
+  </si>
+  <si>
+    <t>string</t>
   </si>
   <si>
     <t>int</t>
-  </si>
-  <si>
-    <t>string</t>
   </si>
 </sst>
 </file>
@@ -974,13 +977,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4" outlineLevelCol="2"/>
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4" outlineLevelCol="3"/>
   <cols>
     <col min="3" max="3" width="18.125" customWidth="1"/>
+    <col min="4" max="4" width="26.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -990,19 +994,25 @@
       <c r="C1" t="s">
         <v>2</v>
       </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:4">
       <c r="A2" t="s">
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:4">
       <c r="A3">
         <v>1</v>
       </c>
@@ -1012,8 +1022,11 @@
       <c r="C3">
         <v>11</v>
       </c>
+      <c r="D3">
+        <v>11</v>
+      </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:4">
       <c r="A4">
         <v>2</v>
       </c>
@@ -1023,8 +1036,11 @@
       <c r="C4">
         <v>22</v>
       </c>
+      <c r="D4">
+        <v>22</v>
+      </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:4">
       <c r="A5">
         <v>3</v>
       </c>
@@ -1032,6 +1048,9 @@
         <v>3</v>
       </c>
       <c r="C5">
+        <v>33</v>
+      </c>
+      <c r="D5">
         <v>33</v>
       </c>
     </row>

--- a/Data/ShopData.xlsx
+++ b/Data/ShopData.xlsx
@@ -212,12 +212,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="34">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF00B050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
@@ -538,7 +544,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -562,16 +568,16 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -580,90 +586,93 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -984,31 +993,31 @@
     <col min="4" max="4" width="26.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" t="s">
+    <row r="1" s="1" customFormat="1" spans="1:4">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4">
-      <c r="A2" t="s">
+    <row r="2" s="1" customFormat="1" spans="1:4">
+      <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="1" t="s">
         <v>4</v>
       </c>
     </row>

--- a/Data/ShopData.xlsx
+++ b/Data/ShopData.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12255"/>
+    <workbookView windowWidth="11430" windowHeight="4485"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="8">
   <si>
     <t>#</t>
   </si>
@@ -40,13 +40,19 @@
     <t>Cost</t>
   </si>
   <si>
-    <t>ImgPath</t>
-  </si>
-  <si>
     <t>string</t>
   </si>
   <si>
     <t>int</t>
+  </si>
+  <si>
+    <t>BeeHive</t>
+  </si>
+  <si>
+    <t>Laser</t>
+  </si>
+  <si>
+    <t>Spear</t>
   </si>
 </sst>
 </file>
@@ -986,14 +992,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4" outlineLevelCol="3"/>
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4" outlineLevelCol="2"/>
   <cols>
     <col min="3" max="3" width="18.125" customWidth="1"/>
     <col min="4" max="4" width="26.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:4">
+    <row r="1" s="1" customFormat="1" spans="1:3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1003,64 +1009,49 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
     </row>
-    <row r="2" s="1" customFormat="1" spans="1:4">
+    <row r="2" s="1" customFormat="1" spans="1:3">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>4</v>
-      </c>
     </row>
-    <row r="3" spans="1:4">
+    <row r="3" spans="1:3">
       <c r="A3">
         <v>1</v>
       </c>
-      <c r="B3">
-        <v>1</v>
+      <c r="B3" t="s">
+        <v>5</v>
       </c>
       <c r="C3">
-        <v>11</v>
-      </c>
-      <c r="D3">
-        <v>11</v>
+        <v>500</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
+    <row r="4" spans="1:3">
       <c r="A4">
         <v>2</v>
       </c>
-      <c r="B4">
-        <v>2</v>
+      <c r="B4" t="s">
+        <v>6</v>
       </c>
       <c r="C4">
-        <v>22</v>
-      </c>
-      <c r="D4">
-        <v>22</v>
+        <v>500</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
+    <row r="5" spans="1:3">
       <c r="A5">
         <v>3</v>
       </c>
-      <c r="B5">
-        <v>3</v>
+      <c r="B5" t="s">
+        <v>7</v>
       </c>
       <c r="C5">
-        <v>33</v>
-      </c>
-      <c r="D5">
-        <v>33</v>
+        <v>500</v>
       </c>
     </row>
   </sheetData>

--- a/Data/ShopData.xlsx
+++ b/Data/ShopData.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="11430" windowHeight="4485"/>
+    <workbookView windowWidth="10665" windowHeight="4440"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="12">
   <si>
     <t>#</t>
   </si>
@@ -38,6 +38,9 @@
   </si>
   <si>
     <t>Cost</t>
+  </si>
+  <si>
+    <t>Info</t>
   </si>
   <si>
     <t>string</t>
@@ -49,10 +52,19 @@
     <t>BeeHive</t>
   </si>
   <si>
+    <t>发射多发导弹追踪目标</t>
+  </si>
+  <si>
     <t>Laser</t>
   </si>
   <si>
+    <t>发射激光持续攻击目标</t>
+  </si>
+  <si>
     <t>Spear</t>
+  </si>
+  <si>
+    <t>连续发射炮弹攻击目标</t>
   </si>
 </sst>
 </file>
@@ -992,14 +1004,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4" outlineLevelCol="2"/>
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" outlineLevelRow="4" outlineLevelCol="3"/>
   <cols>
     <col min="3" max="3" width="18.125" customWidth="1"/>
-    <col min="4" max="4" width="26.25" customWidth="1"/>
+    <col min="4" max="4" width="26.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" spans="1:3">
+    <row r="1" s="1" customFormat="1" spans="1:4">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1009,49 +1021,64 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
     </row>
-    <row r="2" s="1" customFormat="1" spans="1:3">
+    <row r="2" s="1" customFormat="1" spans="1:4">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
+    <row r="3" spans="1:4">
       <c r="A3">
         <v>1</v>
       </c>
       <c r="B3" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C3">
         <v>500</v>
       </c>
+      <c r="D3" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="4" spans="1:3">
+    <row r="4" spans="1:4">
       <c r="A4">
         <v>2</v>
       </c>
       <c r="B4" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C4">
         <v>500</v>
       </c>
+      <c r="D4" t="s">
+        <v>9</v>
+      </c>
     </row>
-    <row r="5" spans="1:3">
+    <row r="5" spans="1:4">
       <c r="A5">
         <v>3</v>
       </c>
       <c r="B5" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C5">
         <v>500</v>
+      </c>
+      <c r="D5" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
